--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projets\Miniprojet-QA\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB7E8FB-55D6-448F-BD6B-BAD4A054AFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9072B942-B82E-4ECC-84C8-82730A8341F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{13BA0E36-25A6-45AD-A3DF-7CF1EDF8E77E}"/>
   </bookViews>
@@ -788,7 +788,7 @@
       <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="4" t="s">

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projets\Miniprojet-QA\test-cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projets\Campagne-QA\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9072B942-B82E-4ECC-84C8-82730A8341F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF01A919-72F0-4174-9141-280707B29601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{13BA0E36-25A6-45AD-A3DF-7CF1EDF8E77E}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>Préconditions</t>
   </si>
   <si>
-    <t>Données d'entré</t>
-  </si>
-  <si>
     <t>Étapes</t>
   </si>
   <si>
@@ -119,10 +116,6 @@
     <t>1. Etre sur la page panier
 2. Supprimer l'item "Combination Pliers"
 3. Verifier que l'item n'est plus dans le panier</t>
-  </si>
-  <si>
-    <t>• Le produit "Combinatio Pliers" ne se trouve plus dans le panier
-• Le montant total est de 0</t>
   </si>
   <si>
     <t>AC-02</t>
@@ -167,18 +160,10 @@
     <t>Produit = "Combination Pliers"</t>
   </si>
   <si>
-    <t>1. Etre sur la page panier
-2. Modifier la quantité de l'item "Combination Pliers" de 1 à 2
-3. L'item à une quantité de 2</t>
-  </si>
-  <si>
     <t>AC-03</t>
   </si>
   <si>
     <t xml:space="preserve">TC-006 </t>
-  </si>
-  <si>
-    <t>Changer la quantité d'item différent</t>
   </si>
   <si>
     <t>• L'utilisateur est sur la page panier
@@ -189,16 +174,6 @@
     <t>1. Etre sur la page panier
 2. Modifier la quantité de l'item A et B de 1 à 2
 3. Chaque item à une quantité de 2</t>
-  </si>
-  <si>
-    <t>• La quantité du produit A et B a changée
-• La quantité du produit A et B est passée de 1 à 2
-• Le montant total à prix en compte les modifications de la quantité</t>
-  </si>
-  <si>
-    <t>• La quantité de l'item "Combination Pliers" a changée
-• La quantité est l'item "Combination Pliers" est à 2
-• Le montant total à prix en compte les modifications</t>
   </si>
   <si>
     <t>TC-007</t>
@@ -221,9 +196,6 @@
 6. Vérifier que le montant total = le prix du produit unitaire</t>
   </si>
   <si>
-    <t>• Le montant total est passé de 0 à au prix du produit unitaire</t>
-  </si>
-  <si>
     <t>TC-008</t>
   </si>
   <si>
@@ -238,17 +210,6 @@
     <t>Produit = "Bolt Cutters"</t>
   </si>
   <si>
-    <t>1. Etre sur la page du produit indisponible
-2. Ajouter le produit au panier
-3. Ouvrir le panier
-4. Appuyer sur le bouton "Proceed to checkout"
-5. Vérifier q'un message d'erreur apparaît</t>
-  </si>
-  <si>
-    <t>• Un message d'erreur apparaît
-• Le processus de paiement ne suit pas son cour</t>
-  </si>
-  <si>
     <t>AC-06</t>
   </si>
   <si>
@@ -262,13 +223,6 @@
     <t>• L'utilisateur est sur la page panier
 • Un item est dans le panier
 • L'utilisateur n'est pas connecté</t>
-  </si>
-  <si>
-    <t>1. Etre sur la page panier
-2. Vérifier que l'item est bien dans le panier
-3. Clic sur le bouton " proceed to checkout"
-4. Etre redirigé sur la page "Sign in"
-4. Etre r</t>
   </si>
   <si>
     <t>• Etre redirigé vers la page "Sign in"</t>
@@ -302,6 +256,51 @@
   </si>
   <si>
     <t>Redirection utilisateur pour suivre le paiement</t>
+  </si>
+  <si>
+    <t>Données d'entrée</t>
+  </si>
+  <si>
+    <t>• Le produit "Combination Pliers" ne se trouve plus dans le panier
+• Le montant total est de 0</t>
+  </si>
+  <si>
+    <t>1. Etre sur la page panier
+2. Modifier la quantité de l'item "Combination Pliers" de 1 à 2
+3. L'item a une quantité de 2</t>
+  </si>
+  <si>
+    <t>• La quantité de l'item "Combination Pliers" a changé
+• La quantité de l'item "Combination Pliers" est à 2
+• Le montant total a pris en compte les modifications</t>
+  </si>
+  <si>
+    <t>Changer la quantité d'items différents</t>
+  </si>
+  <si>
+    <t>• La quantité du produit A et B a changé
+• La quantité du produit A et B est passée de 1 à 2
+• Le montant total a pris en compte les modifications de la quantité</t>
+  </si>
+  <si>
+    <t>• Le montant total est passé de 0 au prix du produit unitaire</t>
+  </si>
+  <si>
+    <t>1. Etre sur la page du produit indisponible
+2. Ajouter le produit au panier
+3. Ouvrir le panier
+4. Appuyer sur le bouton "Proceed to checkout"
+5. Vérifier qu'un message d'erreur apparaît</t>
+  </si>
+  <si>
+    <t>• Un message d'erreur apparaît
+• Le processus de paiement ne suit pas son cours</t>
+  </si>
+  <si>
+    <t>1. Etre sur la page panier
+2. Vérifier que l'item est bien dans le panier
+3. Clic sur le bouton " proceed to checkout"
+4. Etre redirigé sur la page "Sign in"</t>
   </si>
 </sst>
 </file>
@@ -325,7 +324,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -379,12 +378,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -394,13 +396,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -740,13 +745,13 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.19921875" customWidth="1"/>
-    <col min="2" max="2" width="30.265625" customWidth="1"/>
+    <col min="2" max="2" width="26.796875" customWidth="1"/>
     <col min="3" max="3" width="21.3984375" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" customWidth="1"/>
-    <col min="5" max="5" width="17.19921875" customWidth="1"/>
+    <col min="4" max="4" width="19.9296875" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
     <col min="6" max="6" width="23.59765625" customWidth="1"/>
-    <col min="7" max="7" width="5.86328125" customWidth="1"/>
-    <col min="8" max="8" width="4.3984375" customWidth="1"/>
+    <col min="7" max="7" width="5.3984375" customWidth="1"/>
+    <col min="8" max="8" width="5.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -760,279 +765,279 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="32.25" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="42" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="52.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="63" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="53.25" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="74.25" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="84" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="G9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="48" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="10" spans="1:8" ht="63.75" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>11</v>
+      <c r="H10" s="8" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="48.4" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row r="11" spans="1:8" ht="73.5" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="84" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="72" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="72.400000000000006" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="120.4" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="H11" s="8" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="108" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="96.4" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="96" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
